--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olankade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olankade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olankade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>VSSKG</t>
+          <t>VSADA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` (15 hp); rad: - Introduktion omvårdnad och etik - Huvudområde Omvårdnad, 15 hp</t>
+          <t>Programtext `Examensarbete i omvårdnad – demensvård` ≠ kursplanens namn `Examensarbete i omvårdnad - demensvård` (kurskod `AVÅ28V`); rad: - [[AVÅ28V|Examensarbete i omvårdnad – demensvård]], 15 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSADA</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård I - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` (15 hp); rad: - Introduktion omvårdnad och etik - Huvudområde Omvårdnad, 15 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` (10,5 hp); rad: - Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad, 10,5 hp</t>
+          <t>`Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård I - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Människa, hälsa och samhälle - Huvudområde Omvårdnad` (7,5 hp); rad: - Människa, hälsa och samhälle - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` (10,5 hp); rad: - Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad, 10,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` (30 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad, 30 hp</t>
+          <t>`Människa, hälsa och samhälle - Huvudområde Omvårdnad` (7,5 hp); rad: - Människa, hälsa och samhälle - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` (15 hp); rad: - Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` (30 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad, 30 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` (15 hp); rad: - Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad, 15 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Ledarskap och teamarbete - Huvudområde Omvårdnad` (7,5 hp); rad: - Ledarskap och teamarbete - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` (22,5 hp); rad: - Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad, 22,5 hp</t>
+          <t>`Ledarskap och teamarbete - Huvudområde Omvårdnad` (7,5 hp); rad: - Ledarskap och teamarbete - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` (22,5 hp); rad: - Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad, 22,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Examensarbete i omvårdnad - Huvudområde Omvårdnad` (15 hp); rad: - Examensarbete i omvårdnad - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård II - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,17 +973,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>`Examensarbete i omvårdnad - Huvudområde Omvårdnad` (15 hp); rad: - Examensarbete i omvårdnad - Huvudområde Omvårdnad, 15 hp</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>VSSKG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>`Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1023,6 +1050,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
